--- a/moduli_aziende/aifecs/moduli_compilati/MOD-710-A-Ambienti_Lavoro.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-710-A-Ambienti_Lavoro.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R142071aae8434b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cd22fdaf1494d9f"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,6 +447,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cf511514e62495f"/>
 </x:worksheet>
 </file>